--- a/data/BMA_Statements_30_Companies_2023_MILLIONS.xlsx
+++ b/data/BMA_Statements_30_Companies_2023_MILLIONS.xlsx
@@ -2449,6 +2449,66 @@
       <c r="L8" s="4" t="n">
         <v>197.9</v>
       </c>
+      <c r="M8" t="n">
+        <v>336828.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>670980.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>511352</v>
+      </c>
+      <c r="P8" t="n">
+        <v>242133.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>167745.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>146100.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>211034.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>113633.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>137983.9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>97400.39999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>183978.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>75755.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>105517.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>86578.10000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>121750.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>156922.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>64933.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>192095.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>56816.9</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>173156.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2459,16 +2519,96 @@
           <t>Investment Gains/Losses</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
